--- a/HALT_dict_to_translate.xlsx
+++ b/HALT_dict_to_translate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Kilian\Documents\R-Projekte\vocaloidproject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanderki\Documents\vocaloidproject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1488D57B-3EB3-4B11-9757-ADE61DA4E093}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4366086-5EDC-4586-84C2-834CF92CDDEE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="143">
   <si>
     <t>key</t>
   </si>
   <si>
-    <t>de</t>
-  </si>
-  <si>
     <t>de_f</t>
   </si>
   <si>
@@ -98,10 +95,6 @@
   </si>
   <si>
     <t>DEVICE_PROMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;Über welches Gerät gibst Du den Ton in dieser Befragung wieder? &lt;/p&gt;&lt;p&gt;Beispiel: Wenn Du ein Smartphone benutzt, das Du mit Kopfhörern verbunden hast, dann musst Du „Kopfhörer“ auswählen.&lt;/p&gt;&lt;p&gt;Wähle das am ehesten Zutreffende aus.&lt;/p&gt;
-</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;Über welches Gerät geben Sie den Ton in dieser Befragung wieder? &lt;/p&gt;&lt;p&gt;Beispiel: Wenn Sie ein Smartphone benutzen, das Sie mit Kopfhörer verbunden haben, dann müssen Sie „Kopfhörer“ auswählen.&lt;/p&gt;&lt;p&gt;Wählen Sie das am ehesten Zutreffende aus.&lt;/p&gt;
@@ -115,10 +108,6 @@
     <t>SCC_PROMPT_HP</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;Du hast angegeben, dass Du ein anderes Gerät als Kopfhörer zur Tonwiedergabe nutzt. Für diese Befragung ist die Nutzung von Kopfhörern jedoch Grundvoraussetzung.&lt;/p&gt;&lt;p&gt;Im weiteren Verlauf des Fragebogens wurden spezielle Höraufgaben integriert. Mit diesen Aufgaben wird überprüft, ob von den Teilnehmenden wirklich Kopfhörer getragen werden.&lt;/p&gt;&lt;p&gt;Wir bitten Dich daher &lt;strong&gt;AB jetzt unbedingt Kopfhörer zu tragen&lt;/strong&gt;, damit Du die Befragung erfolgreich abschließen kannst. Falls Du ab jetzt keine Kopfhörer trägst, wirst Du im Verlauf der Befragung automatisch aussortiert. In Anbetracht der Länge der Befragung wäre dies sehr ärgerlich.&lt;/p&gt;
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;p&gt;Sie haben angegeben, dass Sie ein anderes Gerät als Kopfhörer zur Tonwiedergabe nutzen. Für diese Befragung ist die Nutzung von Kopfhörern jedoch Grundvoraussetzung.&lt;/p&gt;&lt;p&gt;Im weiteren Verlauf des Fragebogens wurden spezielle Höraufgaben integriert. Mit diesen Aufgaben wird überprüft, ob von den Teilnehmenden wirklich Kopfhörer getragen werden.&lt;/p&gt;&lt;p&gt;Wir bitten Sie daher &lt;strong&gt;AB jetzt unbedingt Kopfhörer zu tragen&lt;/strong&gt;, damit Sie die Befragung erfolgreich abschließen können. Falls Sie ab jetzt keine Kopfhörer tragen, werden Sie im Verlauf der Befragung automatisch aussortiert. In Anbetracht der Länge der Befragung wäre dies sehr ärgerlich.&lt;/p&gt;
 </t>
   </si>
@@ -130,10 +119,6 @@
     <t>SCC_PROMPT_LS</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;Du hast angegeben, dass Du ein anderes Gerät als Lautsprecher zur Tonwiedergabe nutzt. Für diese Befragung ist die Nutzung von Lautsprechern jedoch Grundvoraussetzung.&lt;/p&gt;&lt;p&gt;Im weiteren Verlauf des Fragebogens wurden spezielle Höraufgaben integriert. Mit diesen Aufgaben wird überprüft, ob von den Teilnehmenden wirklich Lautsprecher benutzt werden.&lt;/p&gt;&lt;p&gt;Wir bitten Dich daher &lt;strong&gt;AB jetzt unbedingt Lautsprecher zu benutzen&lt;/strong&gt;, damit Du die Befragung erfolgreich abschließen kannst. Falls Du ab jetzt keine Lautsprecher benutzt, wirst Du im Verlauf der Befragung automatisch aussortiert. In Anbetracht der Länge der Befragung wäre dies sehr ärgerlich.&lt;/p&gt;
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;p&gt;Sie haben angegeben, dass Sie ein anderes Gerät als Lautsprecher zur Tonwiedergabe nutzen. Für diese Befragung ist die Nutzung von Lautsprechern jedoch Grundvoraussetzung.&lt;/p&gt;&lt;p&gt;Im weiteren Verlauf des Fragebogens wurden spezielle Höraufgaben integriert. Mit diesen Aufgaben wird überprüft, ob von den Teilnehmenden wirklich Lautsprecher getragen werden.&lt;/p&gt;&lt;p&gt;Wir bitten Sie daher &lt;strong&gt;AB jetzt unbedingt Lautsprecher zu benutzen&lt;/strong&gt;, damit Sie die Befragung erfolgreich abschließen können. Falls Sie ab jetzt keine Lautsprecher benutzen, werden Sie im Verlauf der Befragung automatisch aussortiert. In Anbetracht der Länge der Befragung wäre dies sehr ärgerlich.&lt;/p&gt;
 </t>
   </si>
@@ -152,12 +137,6 @@
   </si>
   <si>
     <t>STOP_TEXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;die Befragung wurde beendet. Das kann mehrere Gründe haben:&lt;ol&gt;&lt;li&gt;Es haben bereits genügend Probanden mit einem ähnlichen Wiedergabegerät teilgenommen.&lt;/li&gt;&lt;li&gt; Dein Wiedergabegerät ist nicht Teil unserer Zielgruppe.&lt;/li&gt;
-&lt;/ol&gt;Da zukünftige Untersuchungen vielleicht mehr Probanden und andere Zielgruppen erfordern, würden wir uns freuen, Dich in der nächsten Studie wieder begrüßen zu können. &lt;/p&gt;
-&lt;p&gt;Wir bedanken uns für Dein Interesse und Deine Teilnahme.&lt;/p&gt;
-</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;die Befragung wurde beendet. Das kann mehrere Gründe haben:&lt;ol&gt;&lt;li&gt;Es haben bereits genügend Probanden mit einem ähnlichen Wiedergabegerät teilgenommen.&lt;/li&gt;&lt;li&gt; Ihr Wiedergabegerät ist nicht Teil unserer Zielgruppe.&lt;/li&gt;
@@ -198,9 +177,6 @@
     <t>THLT_0001_PROMPT</t>
   </si>
   <si>
-    <t>&lt;h4&gt;Bitte stell die Wiedergabelautstärke entsprechend der Vorgaben ein.&lt;/h4&gt;Wenn Du auf den Play-Button klickst, kannst du leise Rausch-Abschnitte hören. Bitte &lt;strong&gt;stell die Wiedergabe-Lautstärke so ein&lt;/strong&gt;, dass Du alle Rauschabschnitte &lt;strong&gt;noch gerade eben hören kannst&lt;/strong&gt;. Dabei sollte die Einstellung so gewählt werden, dass Du es nicht mehr hören könntest, wenn es etwas leiser wäre.</t>
-  </si>
-  <si>
     <t>&lt;h4&gt;Bitte stellen Sie die Wiedergabelautstärke entsprechend der Vorgaben ein.&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, können Sie leise Rausch-Abschnitte hören. Bitte &lt;strong&gt;stellen Sie die Wiedergabe-Lautstärke so ein&lt;/strong&gt;, dass Sie alle Rauschabschnitte &lt;strong&gt;noch gerade eben hören können&lt;/strong&gt;. Dabei sollte die Einstellung so gewählt werden, dass Sie es nicht mehr hören könnten, wenn es etwas leiser wäre.</t>
   </si>
   <si>
@@ -210,9 +186,6 @@
     <t>THLT_0002_PROMPT</t>
   </si>
   <si>
-    <t>&lt;h4&gt;Wie viele Rauschabschnitte kannst Du hören?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du ein kurzes Audiobeispiel, in dem leise und laute Abschnitte von einem Rauschen zu hören sind. Bitte  &lt;strong&gt;zähle alle leisen und lauten Rauschabschnitte&lt;/strong&gt;  und trage den Zahlenwert in das Textfeld ein.</t>
-  </si>
-  <si>
     <t>&lt;h4&gt;Wie viele Rauschabschnitte können Sie hören?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie ein kurzes Audiobeispiel, in dem leise und laute Abschnitte von einem Rauschen zu hören sind. Bitte  &lt;strong&gt;zählen Sie alle leisen und lauten Rauschabschnitte&lt;/strong&gt;  und tragen Sie den Zahlenwert in das Textfeld ein.</t>
   </si>
   <si>
@@ -220,10 +193,6 @@
   </si>
   <si>
     <t>THLT_0003_PROMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;h4&gt;Wie viele Rauschabschnitte kannst Du hören?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du ein kurzes Audiobeispiel in dem leise und laute Abschnitte von einem Rauschen zu hören sind. Bitte  &lt;strong&gt;zähle alle leisen und lauten Rauschabschnitte&lt;/strong&gt;  und trage den Zahlenwert in das Textfeld ein.&lt;/p&gt;
-</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;p&gt;&lt;h4&gt;Wie viele Rauschabschnitte können Sie hören?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie ein kurzes Audiobeispiel in dem leise und laute Abschnitte von einem Rauschen zu hören sind. Bitte  &lt;strong&gt;zählen Sie alle leisen und lauten Rauschabschnitte&lt;/strong&gt;  und tragen Sie den Zahlenwert in das Textfeld ein.&lt;/p&gt;
@@ -264,10 +233,6 @@
     <t>THLT_0005_PROMPT</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;h4&gt;Wie viele Rausch-Abschnitte kannst Du auf dem rechten Kopfhörer oder Lautsprecher hören?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du sowohl auf dem linken, als auch auf dem rechten Kanal Rausch-Abschnitte. Bitte zähle alle Rauschabschnitte, die Du auf dem &lt;strong&gt;rechten Kopfhörer oder Lautsprecher&lt;/strong&gt; wahrnehmen kannst, und trage die Zahl in das Eingabefeld ein.&lt;/p&gt;
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;p&gt;&lt;h4&gt;Wie viele Rausch-Abschnitte können Sie auf dem rechten Kopfhörer oder Lautsprecher hören?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie sowohl auf dem linken, als auch auf dem rechten Kanal Rausch-Abschnitte. Bitte zählen Sie alle Rauschabschnitte, die Sie auf dem &lt;strong&gt;rechten Kopfhörer oder Lautsprecher&lt;/strong&gt; wahrnehmen können, und tragen Sie die Zahl in das Eingabefeld ein.&lt;/p&gt;
 </t>
   </si>
@@ -313,9 +278,6 @@
   </si>
   <si>
     <t>THLT_0006_PROMPT</t>
-  </si>
-  <si>
-    <t>&lt;h4&gt;Wie bewegt sich das Rauschen?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du ein Rauschsignal, das die wahrgenommene Position über die Zeit verändert. Das Rauschen scheint sich zu bewegen. Wie würdest Du diese Bewegung beschreiben?</t>
   </si>
   <si>
     <t>&lt;h4&gt;Wie bewegt sich das Rauschen?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie ein Rauschsignal, das die wahrgenommene Position über die Zeit verändert. Das Rauschen scheint sich zu bewegen. Wie würden Sie diese Bewegung beschreiben?</t>
@@ -365,9 +327,6 @@
     <t>THLT_0007_PROMPT</t>
   </si>
   <si>
-    <t>&lt;h4&gt;Wo kannst Du das Gehörte lokalisieren?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du einen Ton. Bitte gib an, wo Du den Ton lokalisieren kannst.</t>
-  </si>
-  <si>
     <t>&lt;h4&gt;Wo können Sie das Gehörte lokalisieren?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie einen Ton. Bitte geben Sie an, wo Sie den Ton lokalisieren können.</t>
   </si>
   <si>
@@ -379,9 +338,6 @@
     <t>THLT_0008_PROMPT</t>
   </si>
   <si>
-    <t>&lt;h4&gt;Wie viele Töne kannst Du hören?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du kurze Rauschabschnitte in regelmäßigen Abständen. Neben dem Rauschen sind auch Töne zu hören, die jedoch nie gleichzeitig mit dem Rauschen erklingen. Bitte &lt;strong&gt;zähle nur die gehörten Töne&lt;/strong&gt; und trage den Zahlenwert in das Textfeld ein. &lt;strong&gt;Das Rauschen lässt Du dabei unbeachtet und zählst es auch nicht mit&lt;/strong&gt;.</t>
-  </si>
-  <si>
     <t>&lt;h4&gt;Wie viele Töne können Sie hören?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie kurze Rauschabschnitte in regelmäßigen Abständen. Neben dem Rauschen sind auch Töne zu hören, die jedoch nie gleichzeitig mit dem Rauschen erklingen. Bitte &lt;strong&gt;zählen Sie nur die gehörten Töne&lt;/strong&gt; und tragen Sie den Zahlenwert in das Textfeld ein. &lt;strong&gt;Das Rauschen lassen Sie dabei unbeachtet und zählen es auch nicht mit&lt;/strong&gt;.</t>
   </si>
   <si>
@@ -447,9 +403,6 @@
   </si>
   <si>
     <t>THLT_0013_PROMPT</t>
-  </si>
-  <si>
-    <t>&lt;h4&gt;Welcher Ton ist am leisesten?&lt;/h4&gt;Wenn Du auf den Play-Button klickst, hörst Du ein Audiobeispiel, in dem drei Töne zu hören sind. Diese Töne sind durch kurze Pausen getrennt. Du sollst angeben, welcher Ton für Dich am leisesten klang.</t>
   </si>
   <si>
     <t>&lt;h4&gt;Welcher Ton ist am leisesten?&lt;/h4&gt;Wenn Sie auf den Play-Button klicken, hören Sie ein Audiobeispiel in dem drei Töne zu hören sind. Diese Töne sind durch kurze Pausen getrennt. Sie sollen angeben, welcher Ton für Sie am leisesten klang.</t>
@@ -463,9 +416,6 @@
     <t>WARNING_IMPRECISE</t>
   </si>
   <si>
-    <t>Deine Eingabe war leider falsch. Bitte wiederhole die Aufgabe. Versuche dabei bitte genauer hinzuhören.</t>
-  </si>
-  <si>
     <t>Ihre Eingabe war leider falsch. Bitte wiederholen Sie die Aufgabe. Versuchen Sie dabei bitte genauer hinzuhören.</t>
   </si>
   <si>
@@ -475,9 +425,6 @@
     <t>WARNING_INCORRECT</t>
   </si>
   <si>
-    <t>Deine Eingabe war leider falsch. Bitte wiederhole die Aufgabe.</t>
-  </si>
-  <si>
     <t>Ihre Eingabe war leider falsch. Bitte wiederholen Sie die Aufgabe.</t>
   </si>
   <si>
@@ -487,9 +434,6 @@
     <t>WARNING_TOO_QUIET</t>
   </si>
   <si>
-    <t>Deine Eingabe war leider falsch. Die Wiedergabelautstärke ist vermutlich zu gering. Du kannst die Lautstärke um einen kleinstmöglichen Wert erhöhen und danach die Aufgabe wiederholen.</t>
-  </si>
-  <si>
     <t>Ihre Eingabe war leider falsch. Die Wiedergabelautstärke ist vermutlich zu gering. Sie können die Lautstärke um einen kleinstmöglichen Wert erhöhen und danach die Aufgabe wiederholen.</t>
   </si>
   <si>
@@ -506,13 +450,34 @@
   </si>
   <si>
     <t>not currently</t>
+  </si>
+  <si>
+    <t>参加者 様</t>
+  </si>
+  <si>
+    <t>アンケートは終了しました。終了の理由は以下のいずれかです：&lt;ol&gt;&lt;li&gt;同様の再生デバイスを持つ参加者の数はすでに十分であること。&lt;/li&gt;&lt;li&gt;ご利用の再生機器は、現在の調査対象に含まれていないこと。&lt;/li&gt;&lt;/ol&gt;今後の調査では、より多くの被験者や他の対象グループを求められるようになる可能性があるため、次回の調査でもまたご参加いただければ幸いです。&lt;/p&gt;&lt;p&gt;ご協力とご参加、誠にありがとうございました。&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>音量を調整しました</t>
+  </si>
+  <si>
+    <t>&lt;h4&gt;音は何回聞こえますか？&lt;/h4&gt;&lt;p&gt;再生ボタンをクリックすると、短いオーディオサンプルが再生されます。このサンプルでは、音量が大小いくつの音が含まれています。&lt;strong&gt;音量に関わらず、すべての音を数え&lt;/strong&gt;、その数値をテキストボックスに入力してください。&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>入力が間違っています。再度お試しください。その際は、より注意深くお聞きください。</t>
+  </si>
+  <si>
+    <t>入力が間違っています。再度お試しください。</t>
+  </si>
+  <si>
+    <t>残念ながら、入力が正しくないようです。再生音量が低すぎる可能性があります。音量をほんの少しだけ上げてから、もう一度お試しください。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,13 +493,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -546,16 +523,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Gut" xfId="1" builtinId="26"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -892,20 +872,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="5" width="45.7109375" customWidth="1"/>
+    <col min="3" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="99.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -914,758 +895,644 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="D11" t="s">
+      <c r="B12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E15" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>53</v>
       </c>
-      <c r="D13" t="s">
+      <c r="B16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D16" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" t="s">
         <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" t="s">
-        <v>137</v>
-      </c>
-      <c r="D18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" t="s">
-        <v>139</v>
+      <c r="A18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="A19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D19" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="E19" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B20" t="s">
-        <v>149</v>
-      </c>
-      <c r="C20" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B35" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B36" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C40" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
-      </c>
-      <c r="E40" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
-      </c>
-      <c r="E43" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B44" t="s">
-        <v>149</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D45" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D44" t="s">
-        <v>38</v>
-      </c>
-      <c r="E44" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" t="s">
-        <v>149</v>
-      </c>
-      <c r="C45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" t="s">
-        <v>43</v>
+      <c r="E45" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
